--- a/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Bakery_20260221.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Bakery_20260221.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>16.65</v>
       </c>
       <c r="E2" t="n">
-        <v>16.65</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>16.2</v>
       </c>
       <c r="E3" t="n">
-        <v>97.2</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="4">
@@ -504,6 +504,69 @@
       </c>
       <c r="E4" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>wholeg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Milk - Whole</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>64.31999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skimg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Milk - Skim</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31.12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>twog</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Milk - 2%</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>209.04</v>
       </c>
     </row>
   </sheetData>
